--- a/New folder/(RM)Raw_Material_Purchase_Oder_Planning/GTG_daily_stock_analysis/To_convert_GTG_ITEM_NAME_to_match_our_ITEM_NAME/GTG_Item_type_converion_DB.xlsx
+++ b/New folder/(RM)Raw_Material_Purchase_Oder_Planning/GTG_daily_stock_analysis/To_convert_GTG_ITEM_NAME_to_match_our_ITEM_NAME/GTG_Item_type_converion_DB.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amitk\Desktop\ooffice\New folder\RM_data\PO_lead_time\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\(RM)Raw_Material_Purchase_Oder_Planning\GTG_daily_stock_analysis\To_convert_GTG_ITEM_NAME_to_match_our_ITEM_NAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BC4832-4020-4E69-8A91-E36F8C7391CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{AA0EB75F-1CCE-4480-967A-7122D74F24F0}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RPT_STORESTOCKSTATUS.rpt" sheetId="1" r:id="rId1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="321">
   <si>
     <t xml:space="preserve">Company </t>
   </si>
@@ -996,17 +995,23 @@
   </si>
   <si>
     <t xml:space="preserve"> BLACK DopeDyed</t>
+  </si>
+  <si>
+    <t>1000000230</t>
+  </si>
+  <si>
+    <t>75/2-POLYESTER-YARN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.000_);\-0.000"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="27">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -1167,6 +1172,18 @@
       <color rgb="FFFF0000"/>
       <name val="MS Sans Serif"/>
     </font>
+    <font>
+      <sz val="8.0500000000000007"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1216,7 +1233,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1305,10 +1322,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{7FC4A7DE-BD4E-484B-8F7A-CD3BD1618EE3}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1639,14 +1662,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A9289FD-F0AC-424B-B905-9D62AA0D3557}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:G118"/>
-  <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="256" width="11.5546875" customWidth="1"/>
+    <col min="1" max="256" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1657,7 +1680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1671,7 +1694,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1682,7 +1705,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1702,7 +1725,7 @@
         <v>46240</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="6" t="s">
         <v>10</v>
       </c>
@@ -1725,7 +1748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="8" t="s">
         <v>17</v>
       </c>
@@ -1733,7 +1756,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="9" t="s">
         <v>19</v>
       </c>
@@ -1753,7 +1776,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="9" t="s">
         <v>22</v>
       </c>
@@ -1776,7 +1799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="9" t="s">
         <v>25</v>
       </c>
@@ -1799,7 +1822,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="9" t="s">
         <v>27</v>
       </c>
@@ -1822,7 +1845,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="9" t="s">
         <v>29</v>
       </c>
@@ -1845,7 +1868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="9" t="s">
         <v>31</v>
       </c>
@@ -1868,7 +1891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="9" t="s">
         <v>33</v>
       </c>
@@ -1891,7 +1914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="9" t="s">
         <v>35</v>
       </c>
@@ -1914,7 +1937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" s="9" t="s">
         <v>37</v>
       </c>
@@ -1937,7 +1960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21" s="9" t="s">
         <v>39</v>
       </c>
@@ -1960,7 +1983,7 @@
         <v>2385.6</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="9" t="s">
         <v>41</v>
       </c>
@@ -1983,7 +2006,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" s="9" t="s">
         <v>43</v>
       </c>
@@ -2006,7 +2029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="9" t="s">
         <v>45</v>
       </c>
@@ -2029,7 +2052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" s="9" t="s">
         <v>47</v>
       </c>
@@ -2052,7 +2075,7 @@
         <v>793.35</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" s="9" t="s">
         <v>49</v>
       </c>
@@ -2075,7 +2098,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" s="9" t="s">
         <v>51</v>
       </c>
@@ -2098,7 +2121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" s="9" t="s">
         <v>53</v>
       </c>
@@ -2121,7 +2144,7 @@
         <v>1829.42</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="9" t="s">
         <v>55</v>
       </c>
@@ -2144,7 +2167,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" s="9" t="s">
         <v>57</v>
       </c>
@@ -2167,7 +2190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7">
       <c r="A31" s="9" t="s">
         <v>59</v>
       </c>
@@ -2187,7 +2210,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32" s="9" t="s">
         <v>61</v>
       </c>
@@ -2210,7 +2233,7 @@
         <v>7.62</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7">
       <c r="A33" s="9" t="s">
         <v>63</v>
       </c>
@@ -2233,7 +2256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7">
       <c r="A34" s="9" t="s">
         <v>65</v>
       </c>
@@ -2256,7 +2279,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7">
       <c r="A35" s="9" t="s">
         <v>67</v>
       </c>
@@ -2279,7 +2302,7 @@
         <v>425.9</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7">
       <c r="A36" s="9" t="s">
         <v>69</v>
       </c>
@@ -2302,7 +2325,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7">
       <c r="A37" s="9" t="s">
         <v>71</v>
       </c>
@@ -2325,7 +2348,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7">
       <c r="A38" s="9" t="s">
         <v>73</v>
       </c>
@@ -2348,7 +2371,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7">
       <c r="A39" s="9" t="s">
         <v>75</v>
       </c>
@@ -2368,7 +2391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7">
       <c r="A40" s="9" t="s">
         <v>77</v>
       </c>
@@ -2391,7 +2414,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7">
       <c r="A41" s="9" t="s">
         <v>79</v>
       </c>
@@ -2414,7 +2437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7">
       <c r="A42" s="9" t="s">
         <v>81</v>
       </c>
@@ -2434,7 +2457,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7">
       <c r="A43" s="9" t="s">
         <v>84</v>
       </c>
@@ -2457,7 +2480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7">
       <c r="A44" s="9" t="s">
         <v>86</v>
       </c>
@@ -2480,7 +2503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7">
       <c r="A45" s="9" t="s">
         <v>88</v>
       </c>
@@ -2503,7 +2526,7 @@
         <v>425.72</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7">
       <c r="A46" s="9" t="s">
         <v>90</v>
       </c>
@@ -2526,7 +2549,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7">
       <c r="A47" s="9" t="s">
         <v>92</v>
       </c>
@@ -2549,7 +2572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7">
       <c r="A48" s="9" t="s">
         <v>94</v>
       </c>
@@ -2572,7 +2595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7">
       <c r="A49" s="9" t="s">
         <v>96</v>
       </c>
@@ -2595,7 +2618,7 @@
         <v>977.35</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7">
       <c r="A50" s="9" t="s">
         <v>98</v>
       </c>
@@ -2618,7 +2641,7 @@
         <v>431.8</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7">
       <c r="A51" s="9" t="s">
         <v>100</v>
       </c>
@@ -2641,7 +2664,7 @@
         <v>409.15</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7">
       <c r="A52" s="9" t="s">
         <v>102</v>
       </c>
@@ -2664,7 +2687,7 @@
         <v>100.3</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7">
       <c r="A53" s="9" t="s">
         <v>104</v>
       </c>
@@ -2687,7 +2710,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7">
       <c r="A54" s="9" t="s">
         <v>106</v>
       </c>
@@ -2710,7 +2733,7 @@
         <v>285.78500000000003</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7">
       <c r="A55" s="9" t="s">
         <v>108</v>
       </c>
@@ -2733,7 +2756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7">
       <c r="A56" s="9" t="s">
         <v>110</v>
       </c>
@@ -2756,12 +2779,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7">
       <c r="A57" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7">
       <c r="D58" s="12">
         <v>5649.6549999999997</v>
       </c>
@@ -2775,7 +2798,7 @@
         <v>14084.995000000001</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7">
       <c r="A59" s="8" t="s">
         <v>17</v>
       </c>
@@ -2783,7 +2806,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7">
       <c r="A60" s="9" t="s">
         <v>114</v>
       </c>
@@ -2803,7 +2826,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7">
       <c r="A61" s="9" t="s">
         <v>116</v>
       </c>
@@ -2826,7 +2849,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7">
       <c r="A62" s="9" t="s">
         <v>118</v>
       </c>
@@ -2849,7 +2872,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7">
       <c r="A63" s="9" t="s">
         <v>120</v>
       </c>
@@ -2872,7 +2895,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7">
       <c r="A64" s="9" t="s">
         <v>122</v>
       </c>
@@ -2895,7 +2918,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7">
       <c r="A65" s="9" t="s">
         <v>124</v>
       </c>
@@ -2918,7 +2941,7 @@
         <v>330.7</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7">
       <c r="A66" s="9" t="s">
         <v>126</v>
       </c>
@@ -2941,7 +2964,7 @@
         <v>299.83999999999997</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7">
       <c r="A67" s="9" t="s">
         <v>128</v>
       </c>
@@ -2964,7 +2987,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7">
       <c r="A68" s="9" t="s">
         <v>130</v>
       </c>
@@ -2987,7 +3010,7 @@
         <v>2474</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7">
       <c r="A69" s="9" t="s">
         <v>132</v>
       </c>
@@ -3007,7 +3030,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7">
       <c r="A70" s="9" t="s">
         <v>134</v>
       </c>
@@ -3027,7 +3050,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7">
       <c r="A71" s="9" t="s">
         <v>136</v>
       </c>
@@ -3050,7 +3073,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7">
       <c r="A72" s="9" t="s">
         <v>138</v>
       </c>
@@ -3073,7 +3096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7">
       <c r="A73" s="9" t="s">
         <v>140</v>
       </c>
@@ -3096,7 +3119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7">
       <c r="A74" s="9" t="s">
         <v>142</v>
       </c>
@@ -3119,7 +3142,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7">
       <c r="A75" s="9" t="s">
         <v>144</v>
       </c>
@@ -3142,7 +3165,7 @@
         <v>4140</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7">
       <c r="A76" s="9" t="s">
         <v>146</v>
       </c>
@@ -3165,7 +3188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7">
       <c r="A77" s="9" t="s">
         <v>148</v>
       </c>
@@ -3185,7 +3208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7">
       <c r="A78" s="9" t="s">
         <v>150</v>
       </c>
@@ -3208,7 +3231,7 @@
         <v>1013.93</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7">
       <c r="A79" s="9" t="s">
         <v>152</v>
       </c>
@@ -3231,7 +3254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7">
       <c r="A80" s="9" t="s">
         <v>154</v>
       </c>
@@ -3254,7 +3277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7">
       <c r="A81" s="9" t="s">
         <v>156</v>
       </c>
@@ -3274,7 +3297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7">
       <c r="A82" s="9" t="s">
         <v>158</v>
       </c>
@@ -3297,7 +3320,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7">
       <c r="A83" s="9" t="s">
         <v>160</v>
       </c>
@@ -3317,7 +3340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7">
       <c r="A84" s="9" t="s">
         <v>162</v>
       </c>
@@ -3340,7 +3363,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7">
       <c r="A85" s="9" t="s">
         <v>164</v>
       </c>
@@ -3363,7 +3386,7 @@
         <v>4182.3</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7">
       <c r="A86" s="9" t="s">
         <v>166</v>
       </c>
@@ -3383,7 +3406,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7">
       <c r="A87" s="9" t="s">
         <v>168</v>
       </c>
@@ -3406,7 +3429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7">
       <c r="A88" s="9" t="s">
         <v>170</v>
       </c>
@@ -3429,7 +3452,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7">
       <c r="A89" s="9" t="s">
         <v>172</v>
       </c>
@@ -3452,7 +3475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7">
       <c r="A90" s="9" t="s">
         <v>174</v>
       </c>
@@ -3472,7 +3495,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7">
       <c r="A91" s="9" t="s">
         <v>176</v>
       </c>
@@ -3495,7 +3518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7">
       <c r="A92" s="9" t="s">
         <v>178</v>
       </c>
@@ -3518,7 +3541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7">
       <c r="A93" s="9" t="s">
         <v>180</v>
       </c>
@@ -3535,7 +3558,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7">
       <c r="A94" s="9" t="s">
         <v>182</v>
       </c>
@@ -3552,7 +3575,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7">
       <c r="A95" s="9" t="s">
         <v>184</v>
       </c>
@@ -3575,7 +3598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7">
       <c r="A96" s="9" t="s">
         <v>186</v>
       </c>
@@ -3595,7 +3618,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7">
       <c r="A97" s="9" t="s">
         <v>188</v>
       </c>
@@ -3618,7 +3641,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7">
       <c r="A98" s="9" t="s">
         <v>190</v>
       </c>
@@ -3641,7 +3664,7 @@
         <v>608.09</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7">
       <c r="A99" s="9" t="s">
         <v>192</v>
       </c>
@@ -3661,7 +3684,7 @@
         <v>-7.2759576141834261E-14</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7">
       <c r="A100" s="9" t="s">
         <v>194</v>
       </c>
@@ -3681,7 +3704,7 @@
         <v>652.4</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7">
       <c r="A101" s="9" t="s">
         <v>196</v>
       </c>
@@ -3701,7 +3724,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7">
       <c r="A102" s="9" t="s">
         <v>198</v>
       </c>
@@ -3718,7 +3741,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7">
       <c r="A103" s="9" t="s">
         <v>200</v>
       </c>
@@ -3735,7 +3758,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7">
       <c r="A104" s="9" t="s">
         <v>202</v>
       </c>
@@ -3755,7 +3778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7">
       <c r="A105" s="9" t="s">
         <v>204</v>
       </c>
@@ -3778,7 +3801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7">
       <c r="A106" s="9" t="s">
         <v>206</v>
       </c>
@@ -3795,7 +3818,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7">
       <c r="A107" s="9" t="s">
         <v>208</v>
       </c>
@@ -3815,7 +3838,7 @@
         <v>704.12</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7">
       <c r="A108" s="9" t="s">
         <v>210</v>
       </c>
@@ -3835,7 +3858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7">
       <c r="A109" s="9" t="s">
         <v>212</v>
       </c>
@@ -3858,7 +3881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7">
       <c r="A110" s="9" t="s">
         <v>214</v>
       </c>
@@ -3881,7 +3904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7">
       <c r="A111" s="9" t="s">
         <v>216</v>
       </c>
@@ -3904,7 +3927,7 @@
         <v>329.88</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7">
       <c r="A112" s="9" t="s">
         <v>218</v>
       </c>
@@ -3927,12 +3950,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7">
       <c r="A113" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7">
       <c r="D114" s="12">
         <v>33546.305</v>
       </c>
@@ -3946,7 +3969,7 @@
         <v>24160.78</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7">
       <c r="A115" s="4" t="s">
         <v>220</v>
       </c>
@@ -3963,7 +3986,7 @@
         <v>38245.775000000001</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7">
       <c r="A118" s="13" t="s">
         <v>221</v>
       </c>
@@ -3976,18 +3999,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B5CE927-2808-4323-AFAD-4DEA87E278C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="6" t="s">
         <v>10</v>
       </c>
@@ -4002,7 +4025,7 @@
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="9" t="s">
         <v>19</v>
       </c>
@@ -4016,7 +4039,7 @@
       <c r="E2" s="11"/>
       <c r="G2" s="11"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="9" t="s">
         <v>22</v>
       </c>
@@ -4029,7 +4052,7 @@
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="9" t="s">
         <v>25</v>
       </c>
@@ -4042,7 +4065,7 @@
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="9" t="s">
         <v>27</v>
       </c>
@@ -4055,7 +4078,7 @@
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="9" t="s">
         <v>29</v>
       </c>
@@ -4068,7 +4091,7 @@
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="9" t="s">
         <v>31</v>
       </c>
@@ -4081,7 +4104,7 @@
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="9" t="s">
         <v>33</v>
       </c>
@@ -4094,7 +4117,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="9" t="s">
         <v>35</v>
       </c>
@@ -4107,7 +4130,7 @@
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="9" t="s">
         <v>37</v>
       </c>
@@ -4120,7 +4143,7 @@
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="9" t="s">
         <v>39</v>
       </c>
@@ -4133,7 +4156,7 @@
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="9" t="s">
         <v>41</v>
       </c>
@@ -4146,7 +4169,7 @@
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="9" t="s">
         <v>43</v>
       </c>
@@ -4159,7 +4182,7 @@
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="9" t="s">
         <v>45</v>
       </c>
@@ -4172,7 +4195,7 @@
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="9" t="s">
         <v>47</v>
       </c>
@@ -4185,7 +4208,7 @@
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="9" t="s">
         <v>49</v>
       </c>
@@ -4198,7 +4221,7 @@
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="9" t="s">
         <v>51</v>
       </c>
@@ -4211,7 +4234,7 @@
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="9" t="s">
         <v>53</v>
       </c>
@@ -4224,7 +4247,7 @@
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="9" t="s">
         <v>55</v>
       </c>
@@ -4237,7 +4260,7 @@
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" s="9" t="s">
         <v>57</v>
       </c>
@@ -4250,7 +4273,7 @@
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21" s="9" t="s">
         <v>59</v>
       </c>
@@ -4262,7 +4285,7 @@
       <c r="E21" s="11"/>
       <c r="G21" s="11"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="9" t="s">
         <v>61</v>
       </c>
@@ -4275,7 +4298,7 @@
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" s="9" t="s">
         <v>63</v>
       </c>
@@ -4288,7 +4311,7 @@
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="9" t="s">
         <v>65</v>
       </c>
@@ -4301,7 +4324,7 @@
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" s="9" t="s">
         <v>67</v>
       </c>
@@ -4314,7 +4337,7 @@
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" s="9" t="s">
         <v>69</v>
       </c>
@@ -4327,7 +4350,7 @@
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" s="9" t="s">
         <v>71</v>
       </c>
@@ -4340,7 +4363,7 @@
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" s="9" t="s">
         <v>73</v>
       </c>
@@ -4353,7 +4376,7 @@
       <c r="F28" s="11"/>
       <c r="G28" s="11"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="9" t="s">
         <v>75</v>
       </c>
@@ -4365,7 +4388,7 @@
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" s="9" t="s">
         <v>77</v>
       </c>
@@ -4378,7 +4401,7 @@
       <c r="F30" s="11"/>
       <c r="G30" s="11"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7">
       <c r="A31" s="9" t="s">
         <v>79</v>
       </c>
@@ -4391,7 +4414,7 @@
       <c r="F31" s="11"/>
       <c r="G31" s="11"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32" s="9" t="s">
         <v>81</v>
       </c>
@@ -4403,7 +4426,7 @@
       <c r="E32" s="11"/>
       <c r="G32" s="11"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7">
       <c r="A33" s="9" t="s">
         <v>84</v>
       </c>
@@ -4416,7 +4439,7 @@
       <c r="F33" s="11"/>
       <c r="G33" s="11"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7">
       <c r="A34" s="9" t="s">
         <v>86</v>
       </c>
@@ -4429,7 +4452,7 @@
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7">
       <c r="A35" s="9" t="s">
         <v>88</v>
       </c>
@@ -4442,7 +4465,7 @@
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7">
       <c r="A36" s="9" t="s">
         <v>90</v>
       </c>
@@ -4455,7 +4478,7 @@
       <c r="F36" s="11"/>
       <c r="G36" s="11"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7">
       <c r="A37" s="9" t="s">
         <v>92</v>
       </c>
@@ -4468,7 +4491,7 @@
       <c r="F37" s="11"/>
       <c r="G37" s="11"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7">
       <c r="A38" s="9" t="s">
         <v>94</v>
       </c>
@@ -4481,7 +4504,7 @@
       <c r="F38" s="11"/>
       <c r="G38" s="11"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7">
       <c r="A39" s="9" t="s">
         <v>96</v>
       </c>
@@ -4494,7 +4517,7 @@
       <c r="F39" s="11"/>
       <c r="G39" s="11"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7">
       <c r="A40" s="9" t="s">
         <v>98</v>
       </c>
@@ -4507,7 +4530,7 @@
       <c r="F40" s="11"/>
       <c r="G40" s="11"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7">
       <c r="A41" s="9" t="s">
         <v>100</v>
       </c>
@@ -4520,7 +4543,7 @@
       <c r="F41" s="11"/>
       <c r="G41" s="11"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7">
       <c r="A42" s="9" t="s">
         <v>102</v>
       </c>
@@ -4533,7 +4556,7 @@
       <c r="F42" s="11"/>
       <c r="G42" s="11"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7">
       <c r="A43" s="9" t="s">
         <v>104</v>
       </c>
@@ -4546,7 +4569,7 @@
       <c r="F43" s="11"/>
       <c r="G43" s="11"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7">
       <c r="A44" s="9" t="s">
         <v>106</v>
       </c>
@@ -4559,7 +4582,7 @@
       <c r="F44" s="11"/>
       <c r="G44" s="11"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7">
       <c r="A45" s="9" t="s">
         <v>108</v>
       </c>
@@ -4572,7 +4595,7 @@
       <c r="F45" s="11"/>
       <c r="G45" s="11"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7">
       <c r="A46" s="9" t="s">
         <v>110</v>
       </c>
@@ -4585,7 +4608,7 @@
       <c r="F46" s="11"/>
       <c r="G46" s="11"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7">
       <c r="A47" s="4"/>
     </row>
   </sheetData>
@@ -4594,19 +4617,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{177B866C-E6E5-411B-8118-D61F628545CC}">
-  <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G55"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="26" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="26" customFormat="1">
       <c r="A1" s="23" t="s">
         <v>10</v>
       </c>
@@ -4625,7 +4648,7 @@
       <c r="F1" s="25"/>
       <c r="G1" s="25"/>
     </row>
-    <row r="2" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="21" t="s">
         <v>114</v>
       </c>
@@ -4641,7 +4664,7 @@
       <c r="E2" s="11"/>
       <c r="G2" s="11"/>
     </row>
-    <row r="3" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="21" t="s">
         <v>116</v>
       </c>
@@ -4658,7 +4681,7 @@
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
     </row>
-    <row r="4" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="21" t="s">
         <v>118</v>
       </c>
@@ -4675,7 +4698,7 @@
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
     </row>
-    <row r="5" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="21" t="s">
         <v>120</v>
       </c>
@@ -4692,7 +4715,7 @@
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
     </row>
-    <row r="6" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="21" t="s">
         <v>122</v>
       </c>
@@ -4709,7 +4732,7 @@
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
     </row>
-    <row r="7" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="21" t="s">
         <v>124</v>
       </c>
@@ -4726,7 +4749,7 @@
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
     </row>
-    <row r="8" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="21" t="s">
         <v>126</v>
       </c>
@@ -4743,7 +4766,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
     </row>
-    <row r="9" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="21" t="s">
         <v>128</v>
       </c>
@@ -4760,7 +4783,7 @@
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
     </row>
-    <row r="10" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="21" t="s">
         <v>130</v>
       </c>
@@ -4777,7 +4800,7 @@
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="21" t="s">
         <v>132</v>
       </c>
@@ -4794,7 +4817,7 @@
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
     </row>
-    <row r="12" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="21" t="s">
         <v>134</v>
       </c>
@@ -4811,7 +4834,7 @@
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
     </row>
-    <row r="13" spans="1:7" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" s="32" customFormat="1">
       <c r="A13" s="28" t="s">
         <v>136</v>
       </c>
@@ -4830,7 +4853,7 @@
       <c r="F13" s="31"/>
       <c r="G13" s="31"/>
     </row>
-    <row r="14" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="21" t="s">
         <v>138</v>
       </c>
@@ -4847,7 +4870,7 @@
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
     </row>
-    <row r="15" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="21">
         <v>1000000180</v>
       </c>
@@ -4866,7 +4889,7 @@
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
     </row>
-    <row r="16" spans="1:7" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" s="32" customFormat="1">
       <c r="A16" s="28" t="s">
         <v>142</v>
       </c>
@@ -4885,7 +4908,7 @@
       <c r="F16" s="31"/>
       <c r="G16" s="31"/>
     </row>
-    <row r="17" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="21" t="s">
         <v>144</v>
       </c>
@@ -4902,7 +4925,7 @@
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
     </row>
-    <row r="18" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="21" t="s">
         <v>146</v>
       </c>
@@ -4921,7 +4944,7 @@
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
     </row>
-    <row r="19" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="21" t="s">
         <v>148</v>
       </c>
@@ -4938,7 +4961,7 @@
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" s="21" t="s">
         <v>150</v>
       </c>
@@ -4955,7 +4978,7 @@
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
     </row>
-    <row r="21" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21" s="21" t="s">
         <v>152</v>
       </c>
@@ -4971,7 +4994,7 @@
       <c r="E21" s="11"/>
       <c r="G21" s="11"/>
     </row>
-    <row r="22" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="21" t="s">
         <v>154</v>
       </c>
@@ -4990,7 +5013,7 @@
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
     </row>
-    <row r="23" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" s="21" t="s">
         <v>156</v>
       </c>
@@ -5007,7 +5030,7 @@
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="21" t="s">
         <v>158</v>
       </c>
@@ -5024,7 +5047,7 @@
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
     </row>
-    <row r="25" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" s="21" t="s">
         <v>160</v>
       </c>
@@ -5041,7 +5064,7 @@
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
     </row>
-    <row r="26" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" s="21" t="s">
         <v>162</v>
       </c>
@@ -5058,7 +5081,7 @@
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
     </row>
-    <row r="27" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" s="21" t="s">
         <v>164</v>
       </c>
@@ -5075,7 +5098,7 @@
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
     </row>
-    <row r="28" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" s="21" t="s">
         <v>166</v>
       </c>
@@ -5092,7 +5115,7 @@
       <c r="F28" s="11"/>
       <c r="G28" s="11"/>
     </row>
-    <row r="29" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="21" t="s">
         <v>168</v>
       </c>
@@ -5108,7 +5131,7 @@
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
     </row>
-    <row r="30" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" s="21" t="s">
         <v>170</v>
       </c>
@@ -5125,7 +5148,7 @@
       <c r="F30" s="11"/>
       <c r="G30" s="11"/>
     </row>
-    <row r="31" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7">
       <c r="A31" s="21" t="s">
         <v>172</v>
       </c>
@@ -5142,7 +5165,7 @@
       <c r="F31" s="11"/>
       <c r="G31" s="11"/>
     </row>
-    <row r="32" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32" s="21" t="s">
         <v>174</v>
       </c>
@@ -5158,7 +5181,7 @@
       <c r="E32" s="11"/>
       <c r="G32" s="11"/>
     </row>
-    <row r="33" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7">
       <c r="A33" s="21" t="s">
         <v>176</v>
       </c>
@@ -5175,7 +5198,7 @@
       <c r="F33" s="11"/>
       <c r="G33" s="11"/>
     </row>
-    <row r="34" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7">
       <c r="A34" s="21" t="s">
         <v>178</v>
       </c>
@@ -5192,7 +5215,7 @@
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
     </row>
-    <row r="35" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7">
       <c r="A35" s="21" t="s">
         <v>180</v>
       </c>
@@ -5209,7 +5232,7 @@
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
     </row>
-    <row r="36" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7">
       <c r="A36" s="21" t="s">
         <v>182</v>
       </c>
@@ -5226,7 +5249,7 @@
       <c r="F36" s="11"/>
       <c r="G36" s="11"/>
     </row>
-    <row r="37" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7">
       <c r="A37" s="21" t="s">
         <v>184</v>
       </c>
@@ -5243,7 +5266,7 @@
       <c r="F37" s="11"/>
       <c r="G37" s="11"/>
     </row>
-    <row r="38" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7">
       <c r="A38" s="21" t="s">
         <v>186</v>
       </c>
@@ -5262,7 +5285,7 @@
       <c r="F38" s="11"/>
       <c r="G38" s="11"/>
     </row>
-    <row r="39" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7">
       <c r="A39" s="21" t="s">
         <v>188</v>
       </c>
@@ -5279,7 +5302,7 @@
       <c r="F39" s="11"/>
       <c r="G39" s="11"/>
     </row>
-    <row r="40" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7">
       <c r="A40" s="21" t="s">
         <v>190</v>
       </c>
@@ -5296,7 +5319,7 @@
       <c r="F40" s="11"/>
       <c r="G40" s="11"/>
     </row>
-    <row r="41" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7">
       <c r="A41" s="21" t="s">
         <v>192</v>
       </c>
@@ -5313,7 +5336,7 @@
       <c r="F41" s="11"/>
       <c r="G41" s="11"/>
     </row>
-    <row r="42" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7">
       <c r="A42" s="21" t="s">
         <v>194</v>
       </c>
@@ -5330,7 +5353,7 @@
       <c r="F42" s="11"/>
       <c r="G42" s="11"/>
     </row>
-    <row r="43" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7">
       <c r="A43" s="21" t="s">
         <v>196</v>
       </c>
@@ -5347,7 +5370,7 @@
       <c r="F43" s="11"/>
       <c r="G43" s="11"/>
     </row>
-    <row r="44" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7">
       <c r="A44" s="21" t="s">
         <v>198</v>
       </c>
@@ -5364,7 +5387,7 @@
       <c r="F44" s="11"/>
       <c r="G44" s="11"/>
     </row>
-    <row r="45" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7">
       <c r="A45" s="21" t="s">
         <v>200</v>
       </c>
@@ -5381,7 +5404,7 @@
       <c r="F45" s="11"/>
       <c r="G45" s="11"/>
     </row>
-    <row r="46" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7">
       <c r="A46" s="21" t="s">
         <v>202</v>
       </c>
@@ -5398,7 +5421,7 @@
       <c r="F46" s="11"/>
       <c r="G46" s="11"/>
     </row>
-    <row r="47" spans="1:7" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" s="32" customFormat="1">
       <c r="A47" s="28" t="s">
         <v>204</v>
       </c>
@@ -5412,7 +5435,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" s="32" customFormat="1">
       <c r="A48" s="28" t="s">
         <v>206</v>
       </c>
@@ -5426,7 +5449,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4">
       <c r="A49" s="21" t="s">
         <v>208</v>
       </c>
@@ -5440,7 +5463,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4">
       <c r="A50" s="21" t="s">
         <v>210</v>
       </c>
@@ -5454,7 +5477,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4">
       <c r="A51" s="21" t="s">
         <v>212</v>
       </c>
@@ -5468,7 +5491,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4">
       <c r="A52" s="21" t="s">
         <v>214</v>
       </c>
@@ -5482,7 +5505,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4">
       <c r="A53" s="21" t="s">
         <v>216</v>
       </c>
@@ -5496,7 +5519,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4">
       <c r="A54" s="21" t="s">
         <v>218</v>
       </c>
@@ -5510,23 +5533,34 @@
         <v>311</v>
       </c>
     </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="36" t="s">
+        <v>319</v>
+      </c>
+      <c r="B55" s="37" t="s">
+        <v>320</v>
+      </c>
+      <c r="C55" s="32" t="s">
+        <v>309</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C54" xr:uid="{177B866C-E6E5-411B-8118-D61F628545CC}"/>
+  <autoFilter ref="A1:C54"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD9BA6A-44C3-443F-BFB6-84E0DA41E5C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H90"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="45.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="54.33203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15">
       <c r="A1" s="14" t="s">
         <v>222</v>
       </c>
@@ -5534,7 +5568,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15">
       <c r="A2" s="15" t="s">
         <v>223</v>
       </c>
@@ -5542,7 +5576,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15">
       <c r="A3" s="14" t="s">
         <v>224</v>
       </c>
@@ -5550,7 +5584,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15">
       <c r="A4" s="14" t="s">
         <v>223</v>
       </c>
@@ -5558,7 +5592,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15">
       <c r="A5" s="14" t="s">
         <v>223</v>
       </c>
@@ -5566,7 +5600,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15">
       <c r="A6" s="14" t="s">
         <v>222</v>
       </c>
@@ -5574,7 +5608,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15">
       <c r="A7" s="14" t="s">
         <v>222</v>
       </c>
@@ -5582,7 +5616,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15">
       <c r="A8" s="14" t="s">
         <v>222</v>
       </c>
@@ -5590,7 +5624,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15">
       <c r="A9" s="14" t="s">
         <v>225</v>
       </c>
@@ -5598,7 +5632,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15">
       <c r="A10" s="14" t="s">
         <v>226</v>
       </c>
@@ -5606,7 +5640,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15">
       <c r="A11" s="14" t="s">
         <v>227</v>
       </c>
@@ -5614,7 +5648,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15">
       <c r="A12" s="14" t="s">
         <v>227</v>
       </c>
@@ -5622,7 +5656,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="15">
       <c r="A13" s="14" t="s">
         <v>227</v>
       </c>
@@ -5630,7 +5664,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="15">
       <c r="A14" s="14" t="s">
         <v>228</v>
       </c>
@@ -5638,7 +5672,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="15">
       <c r="A15" s="14" t="s">
         <v>229</v>
       </c>
@@ -5646,7 +5680,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="15">
       <c r="A16" s="14" t="s">
         <v>230</v>
       </c>
@@ -5654,7 +5688,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15">
       <c r="A17" s="14" t="s">
         <v>231</v>
       </c>
@@ -5662,7 +5696,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15">
       <c r="A18" s="15" t="s">
         <v>232</v>
       </c>
@@ -5670,7 +5704,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="15">
       <c r="A19" s="15" t="s">
         <v>233</v>
       </c>
@@ -5678,7 +5712,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15">
       <c r="A20" s="15" t="s">
         <v>234</v>
       </c>
@@ -5686,7 +5720,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15">
       <c r="A21" s="14" t="s">
         <v>231</v>
       </c>
@@ -5694,7 +5728,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15">
       <c r="A22" s="16" t="s">
         <v>229</v>
       </c>
@@ -5702,7 +5736,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15">
       <c r="A23" s="14" t="s">
         <v>230</v>
       </c>
@@ -5710,7 +5744,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15">
       <c r="A24" s="14" t="s">
         <v>231</v>
       </c>
@@ -5718,7 +5752,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="15">
       <c r="A25" s="14" t="s">
         <v>230</v>
       </c>
@@ -5726,7 +5760,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="15">
       <c r="A26" s="14" t="s">
         <v>231</v>
       </c>
@@ -5734,7 +5768,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="15">
       <c r="A27" s="15" t="s">
         <v>235</v>
       </c>
@@ -5742,7 +5776,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="15">
       <c r="A28" s="17" t="s">
         <v>236</v>
       </c>
@@ -5750,7 +5784,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="15">
       <c r="A29" s="17" t="s">
         <v>237</v>
       </c>
@@ -5758,7 +5792,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="15">
       <c r="A30" s="17" t="s">
         <v>238</v>
       </c>
@@ -5766,7 +5800,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="15">
       <c r="A31" s="17" t="s">
         <v>239</v>
       </c>
@@ -5774,7 +5808,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="15">
       <c r="A32" s="14" t="s">
         <v>240</v>
       </c>
@@ -5782,7 +5816,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="15">
       <c r="A33" s="14" t="s">
         <v>240</v>
       </c>
@@ -5790,7 +5824,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="15">
       <c r="A34" s="14" t="s">
         <v>240</v>
       </c>
@@ -5798,7 +5832,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="15">
       <c r="A35" s="18" t="s">
         <v>241</v>
       </c>
@@ -5806,7 +5840,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="15">
       <c r="A36" s="18" t="s">
         <v>242</v>
       </c>
@@ -5814,7 +5848,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="15">
       <c r="A37" s="18" t="s">
         <v>242</v>
       </c>
@@ -5822,7 +5856,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="15">
       <c r="A38" s="15" t="s">
         <v>243</v>
       </c>
@@ -5830,7 +5864,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="15">
       <c r="A39" s="15" t="s">
         <v>241</v>
       </c>
@@ -5838,7 +5872,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="15">
       <c r="A40" s="14" t="s">
         <v>241</v>
       </c>
@@ -5846,7 +5880,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="15">
       <c r="A41" s="14" t="s">
         <v>241</v>
       </c>
@@ -5854,7 +5888,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="15">
       <c r="A42" s="14" t="s">
         <v>240</v>
       </c>
@@ -5862,7 +5896,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="15">
       <c r="A43" s="14" t="s">
         <v>244</v>
       </c>
@@ -5870,7 +5904,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="15">
       <c r="A44" s="14" t="s">
         <v>244</v>
       </c>
@@ -5878,7 +5912,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="15">
       <c r="A45" s="14" t="s">
         <v>244</v>
       </c>
@@ -5886,7 +5920,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="15">
       <c r="A46" s="14" t="s">
         <v>244</v>
       </c>
@@ -5894,7 +5928,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="15">
       <c r="A47" s="14" t="s">
         <v>244</v>
       </c>
@@ -5902,7 +5936,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="15">
       <c r="A48" s="14" t="s">
         <v>245</v>
       </c>
@@ -5910,7 +5944,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="15">
       <c r="A49" s="14" t="s">
         <v>244</v>
       </c>
@@ -5918,7 +5952,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="15">
       <c r="A50" s="14" t="s">
         <v>246</v>
       </c>
@@ -5926,7 +5960,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="15">
       <c r="A51" s="14" t="s">
         <v>246</v>
       </c>
@@ -5934,7 +5968,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="15">
       <c r="A52" s="19" t="s">
         <v>247</v>
       </c>
@@ -5942,7 +5976,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="15">
       <c r="A53" s="18" t="s">
         <v>248</v>
       </c>
@@ -5950,7 +5984,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15">
       <c r="A54" s="19" t="s">
         <v>244</v>
       </c>
@@ -5958,77 +5992,77 @@
         <v>286</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15">
       <c r="A55" s="19" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15">
       <c r="A56" s="18" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="15">
       <c r="A57" s="18" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" ht="15">
       <c r="A58" s="19" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" ht="15">
       <c r="A59" s="14" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" ht="15">
       <c r="A60" s="19" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" ht="15">
       <c r="A61" s="18" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" ht="15">
       <c r="A62" s="14" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" ht="15">
       <c r="A63" s="14" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" ht="15">
       <c r="A64" s="14" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="15">
       <c r="A65" s="14" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="15">
       <c r="A66" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="15">
       <c r="A67" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="15">
       <c r="A68" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="15">
       <c r="A69" s="14" t="s">
         <v>253</v>
       </c>
@@ -6039,7 +6073,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="15">
       <c r="A70" s="15" t="s">
         <v>253</v>
       </c>
@@ -6050,7 +6084,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="15">
       <c r="A71" s="14" t="s">
         <v>253</v>
       </c>
@@ -6061,7 +6095,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="15">
       <c r="A72" s="14" t="s">
         <v>254</v>
       </c>
@@ -6072,92 +6106,92 @@
         <v>210</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="15">
       <c r="A73" s="14" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="15">
       <c r="A74" s="15" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="15">
       <c r="A75" s="17" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="15">
       <c r="A76" s="17" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="15">
       <c r="A77" s="14" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" ht="15">
       <c r="A78" s="14" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" ht="15">
       <c r="A79" s="19" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" ht="15">
       <c r="A80" s="19" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="81" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:1" ht="15">
       <c r="A81" s="14" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="82" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:1" ht="15">
       <c r="A82" s="14" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="83" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:1" ht="15">
       <c r="A83" s="14" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="84" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:1" ht="15">
       <c r="A84" s="14" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="85" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:1" ht="15">
       <c r="A85" s="14" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="86" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:1" ht="15">
       <c r="A86" s="14" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="87" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:1" ht="15">
       <c r="A87" s="17" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="88" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:1" ht="15">
       <c r="A88" s="17" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="89" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:1" ht="15">
       <c r="A89" s="20" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="90" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:1" ht="15">
       <c r="A90" s="17" t="s">
         <v>238</v>
       </c>
